--- a/app/src/main/assets/invoice_template.xlsx
+++ b/app/src/main/assets/invoice_template.xlsx
@@ -729,15 +729,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>109856</xdr:colOff>
+      <xdr:colOff>111063</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>10864</xdr:rowOff>
+      <xdr:rowOff>24445</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>995953</xdr:colOff>
+      <xdr:colOff>997160</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>164306</xdr:rowOff>
+      <xdr:rowOff>177700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -773,15 +773,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>42252</xdr:colOff>
+      <xdr:colOff>43459</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>5000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>383894</xdr:colOff>
+      <xdr:colOff>385101</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>322138</xdr:rowOff>
+      <xdr:rowOff>151447</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -817,15 +817,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>330777</xdr:colOff>
+      <xdr:colOff>331984</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1530194</xdr:colOff>
+      <xdr:colOff>1532262</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>234582</xdr:rowOff>
+      <xdr:rowOff>102869</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1122,7 +1122,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:L33"/>
+  <dimension ref="B1:K33"/>
   <sheetFormatPr defaultRowHeight="13.8" defaultColWidth="10"/>
   <cols>
     <col min="1" max="2" customWidth="1" width="1.5976562" style="0"/>
@@ -1399,7 +1399,7 @@
       <c r="G27" s="56"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="8:8">
+    <row r="28" spans="8:8" ht="13.8">
       <c r="B28" s="4"/>
       <c r="C28" s="57" t="s">
         <v>12</v>
@@ -1410,7 +1410,7 @@
       <c r="G28" s="57"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="8:8" ht="33.3" customHeight="1">
+    <row r="29" spans="8:8" ht="14.4">
       <c r="B29" s="58"/>
       <c r="C29" s="59"/>
       <c r="D29" s="59"/>
@@ -1419,10 +1419,12 @@
       <c r="G29" s="59"/>
       <c r="H29" s="60"/>
     </row>
+    <row r="30" spans="8:8" ht="13.8"/>
+    <row r="31" spans="8:8" ht="13.8"/>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="F25:G25"/>
@@ -1430,13 +1432,13 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:G27"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E12:G12"/>
     <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E14:G14"/>
     <mergeCell ref="C5:G5"/>
   </mergeCells>
   <pageMargins left="0.06" right="0.25" top="0.38" bottom="0.32" header="0.3" footer="0.3"/>

--- a/app/src/main/assets/invoice_template.xlsx
+++ b/app/src/main/assets/invoice_template.xlsx
@@ -154,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -355,9 +355,29 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -531,7 +551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -658,61 +678,64 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -729,15 +752,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>111063</xdr:colOff>
+      <xdr:colOff>107442</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>24445</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>997160</xdr:colOff>
+      <xdr:colOff>993538</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>177700</xdr:rowOff>
+      <xdr:rowOff>139303</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -773,15 +796,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>43459</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>5000</xdr:rowOff>
+      <xdr:colOff>39838</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>29438</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>385101</xdr:colOff>
+      <xdr:colOff>379065</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>151447</xdr:rowOff>
+      <xdr:rowOff>147875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -797,8 +820,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="151085" y="9281948"/>
-          <a:ext cx="1392621" cy="343545"/>
+          <a:off x="291428" y="12756406"/>
+          <a:ext cx="1575236" cy="293660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -817,15 +840,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>331984</xdr:colOff>
+      <xdr:colOff>15693</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1532262</xdr:colOff>
+      <xdr:colOff>2035121</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>102869</xdr:rowOff>
+      <xdr:rowOff>164306</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -841,8 +864,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3593223" y="9268813"/>
-          <a:ext cx="2253156" cy="243049"/>
+          <a:off x="3975234" y="12902209"/>
+          <a:ext cx="3255235" cy="164286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1122,14 +1145,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K33"/>
+  <dimension ref="B1:N45"/>
   <sheetFormatPr defaultRowHeight="13.8" defaultColWidth="10"/>
   <cols>
     <col min="1" max="2" customWidth="1" width="1.5976562" style="0"/>
     <col min="3" max="6" customWidth="1" width="15.699219" style="0"/>
-    <col min="7" max="7" customWidth="1" width="26.898438" style="0"/>
-    <col min="8" max="8" customWidth="1" width="1.3984375" style="0"/>
-    <col min="9" max="9" customWidth="1" width="0.8984375" style="0"/>
+    <col min="7" max="7" customWidth="1" width="48.92578" style="0"/>
+    <col min="8" max="8" customWidth="1" width="3.6445312" style="0"/>
+    <col min="9" max="9" customWidth="1" width="22.125" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="8:8" ht="14.4"/>
@@ -1272,101 +1295,101 @@
       <c r="B15" s="4"/>
       <c r="C15" s="39"/>
       <c r="D15" s="40"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="8:8" ht="53.25" customHeight="1">
       <c r="B16" s="4"/>
       <c r="C16" s="39"/>
       <c r="D16" s="40"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="8:8" ht="53.25" customHeight="1">
       <c r="B17" s="4"/>
       <c r="C17" s="39"/>
       <c r="D17" s="40"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="8"/>
     </row>
     <row r="18" spans="8:8" ht="53.25" customHeight="1">
       <c r="B18" s="4"/>
       <c r="C18" s="39"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="8:8" ht="53.25" customHeight="1">
       <c r="B19" s="4"/>
       <c r="C19" s="39"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="8"/>
     </row>
     <row r="20" spans="8:8" ht="53.25" customHeight="1">
       <c r="B20" s="4"/>
       <c r="C20" s="39"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="8:8" ht="53.25" customHeight="1">
       <c r="B21" s="4"/>
       <c r="C21" s="39"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="8"/>
     </row>
     <row r="22" spans="8:8" ht="53.25" customHeight="1">
       <c r="B22" s="4"/>
       <c r="C22" s="39"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="8"/>
     </row>
     <row r="23" spans="8:8" ht="53.25" customHeight="1">
       <c r="B23" s="4"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="8:8" ht="16.45">
       <c r="B24" s="4"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="46" t="s">
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="48"/>
+      <c r="G24" s="49"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" spans="8:8" ht="16.45">
       <c r="B25" s="4"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="51" t="s">
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52" t="s">
         <v>5</v>
       </c>
       <c r="F25" s="36" t="s">
@@ -1382,64 +1405,77 @@
       <c r="E26" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="52" t="s">
+      <c r="F26" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="53"/>
+      <c r="G26" s="54"/>
       <c r="H26" s="8"/>
     </row>
     <row r="27" spans="8:8" ht="33.75" customHeight="1">
       <c r="B27" s="4"/>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="57"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="8:8" ht="13.8">
+    <row r="28" spans="8:8">
       <c r="B28" s="4"/>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="8:8" ht="14.4">
-      <c r="B29" s="58"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="60"/>
-    </row>
-    <row r="30" spans="8:8" ht="13.8"/>
-    <row r="31" spans="8:8" ht="13.8"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+    </row>
+    <row r="36" spans="8:8" ht="13.85">
+      <c r="C36"/>
+    </row>
+    <row r="45" spans="8:8" ht="13.85">
+      <c r="C45"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="26">
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="C4:G4"/>
     <mergeCell ref="E7:G7"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="E17:G17"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E19:G19"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <pageMargins left="0.06" right="0.25" top="0.38" bottom="0.32" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="92"/>
